--- a/spectakeoff/ECISD_Closeout_Schedule.xlsx
+++ b/spectakeoff/ECISD_Closeout_Schedule.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,10 +97,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source: ECISD.pdf (234 pages) - 26 requirements. Every quote verified word-for-word against the cited page.</t>
+          <t>Source: ECISD.pdf (234 pages) - 25 requirements. Every quote verified word-for-word against the cited page.</t>
         </is>
       </c>
     </row>
@@ -569,47 +569,45 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>01 50 00</t>
+          <t>01 77 00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>TEMPORARY FACILITIES AND CONTROLS</t>
+          <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Special Tool</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Owner with one set of keys</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
+          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Provide Owner with one set of keys.</t>
+          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
@@ -632,7 +630,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel</t>
+          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
@@ -643,64 +641,60 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel.</t>
+          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="n">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Make final changeover of permanent locks and deliver keys to Owner</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner.</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Make final changeover of permanent locks and deliver keys to Owner.</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -720,26 +714,30 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Make final changeover of permanent locks and deliver keys to Owner</t>
+          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Make final changeover of permanent locks and deliver keys to Owner.</t>
+          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
@@ -762,30 +760,30 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
+          <t>additional copies of each warranty to include in operation and maintenance manuals</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>of each warranty to include in operation and maintenance manuals</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems.</t>
+          <t>Provide additional copies of each warranty to include in operation and maintenance manuals.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
@@ -793,114 +791,124 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>01 77 00</t>
+          <t>01 78 23</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CLOSEOUT PROCEDURES</t>
+          <t>OPERATION AND MAINTENANCE DATA</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>additional copies of each warranty to include in operation and maintenance manuals</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="inlineStr"/>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>of each warranty to include in operation and maintenance manuals</t>
+          <t>of each manual in final form at least 15 days before final inspection</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Provide additional copies of each warranty to include in operation and maintenance manuals.</t>
+          <t>Manual: Submit one copy of each manual in final form at least 15 days before final inspection.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>01 78 23</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>OPERATION AND MAINTENANCE DATA</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>3 copies of each corrected manual within 15 days of receipt of Engineer's comments</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>of each manual in final form at least 15 days before final inspection</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>of each corrected manual within 15 days of receipt of Engineer's comments</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Manual: Submit one copy of each manual in final form at least 15 days before final inspection.</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Submit 3 copies of each corrected manual within 15 days of receipt of Engineer's comments.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>01 78 23</t>
+          <t>01 78 39</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>OPERATION AND MAINTENANCE DATA</t>
+          <t>PROJECT RECORD DOCUMENTS</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -910,91 +918,83 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>3 copies of each corrected manual within 15 days of receipt of Engineer's comments</t>
+          <t>Number of Copies</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>of each corrected manual within 15 days of receipt of Engineer's comments</t>
-        </is>
-      </c>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Submit 3 copies of each corrected manual within 15 days of receipt of Engineer's comments.</t>
+          <t>Number of Copies: Submit one set of marked-up Record Prints.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>01 78 39</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>PROJECT RECORD DOCUMENTS</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Number of Copies</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Record Specifications</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="n">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Number of Copies: Submit one set of marked-up Record Prints.</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Record Specifications: Submit one copy of Project's Specifications, including addenda and contract modifications.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Record Specifications</t>
+          <t>Record Product Data</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -1025,380 +1025,388 @@
           <t>EA</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>of each Product Data submittal</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="n">
         <v>73</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Record Specifications: Submit one copy of Project's Specifications, including addenda and contract modifications.</t>
+          <t>Record Product Data: Submit one copy of each Product Data submittal.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>01 78 39</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>PROJECT RECORD DOCUMENTS</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DEMONSTRATION AND TRAINING</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This Section includes administrative and procedural requirements for instructing Owner's personnel, including </t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>This Section includes administrative and procedural requirements for instructing Owner's personnel, including the following:</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DEMONSTRATION AND TRAINING</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Record Product Data</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Instruction Program</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>of each Product Data submittal</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Record Product Data: Submit one copy of each Product Data submittal.</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>for each training module</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Instruction Program: Submit two copies of outline of instructional program for demonstration and training, including a schedule of proposed dates, times, length of instruction time, and instructors' names for each training module.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This Section includes administrative and procedural requirements for instructing Owner's personnel, including </t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>This Section includes administrative and procedural requirements for instructing Owner's personnel, including the following:</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Facilitator</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Facilitator: Engage a qualified facilitator to prepare instruction program and training modules, to coordinate instructors, and to coordinate between Contractor and Owner for number of participants, instruction times, and location.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Instruction Program</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>for each training module</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Instruction Program: Submit two copies of outline of instructional program for demonstration and training, including a schedule of proposed dates, times, length of instruction time, and instructors' names for each training module.</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystem</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystems, and equipment not part of a system.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DEMONSTRATION AND TRAINING</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>of each season</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>DEMONSTRATION AND TRAINING</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Schedule training with Owner with at least seven days' advance notice</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Schedule training with Owner with at least seven days' advance notice.</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>09911</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>EXTERIOR PAINTING</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Paint</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>of each material and color applied</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Paint: 5 percent, but not less than 1 gal. of each material and color applied.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Facilitator</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Facilitator: Engage a qualified facilitator to prepare instruction program and training modules, to coordinate instructors, and to coordinate between Contractor and Owner for number of participants, instruction times, and location.</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystem</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystems, and equipment not part of a system.</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>of each season</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season.</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Schedule training with Owner with at least seven days' advance notice</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Schedule training with Owner with at least seven days' advance notice.</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>09911</t>
+          <t>09912</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>EXTERIOR PAINTING</t>
+          <t>INTERIOR PAINTING</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1412,87 +1420,79 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>PCT</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>of each material and color applied</t>
-        </is>
-      </c>
+      <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Paint: 5 percent, but not less than 1 gal. of each material and color applied.</t>
+          <t>Paint: 2 percent, but not less than 1 gal.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>09912</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>INTERIOR PAINTING</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Paint</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>PCT</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Paint: 2 percent, but not less than 1 gal.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from date of acceptance of the job.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1507,37 +1507,35 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Upon completion of the work and at a time designated by the Owner's representative, provide a formal training </t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from date of acceptance of the job.</t>
+          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training session for the Owner's operating personnel to include location, operation, and maintenance of all mechanical equipment and systems.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
       <c r="N22" s="3" t="n"/>
@@ -1555,132 +1553,134 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upon completion of the work and at a time designated by the Owner's representative, provide a formal training </t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>Owner's Manual</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training session for the Owner's operating personnel to include location, operation, and maintenance of all mechanical equipment and systems.</t>
+          <t>Owner's Manual: Prior to final acceptance, provide two bound volumes to the Architect.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL GENERAL REQUIREMENTS</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Owner's Manual</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Owner's Manual: Prior to final acceptance, provide two bound volumes to the Architect.</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>15181</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>HYDRONIC PIPING</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Water Treatment Chemicals</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>from date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Water Treatment Chemicals: Furnish sufficient chemicals for initial system startup and for preventive maintenance for one year from date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>15181</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>HYDRONIC PIPING</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Water Treatment Chemicals</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>from date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Water Treatment Chemicals: Furnish sufficient chemicals for initial system startup and for preventive maintenance for one year from date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>15625</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whi</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Provide a full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whichever occurs first.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1695,147 +1695,101 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whi</t>
+          <t xml:space="preserve">In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and </t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="n">
         <v>206</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Provide a full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whichever occurs first.</t>
+          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and maintenance of Applied Chillers for 1 years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
       <c r="N26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and </t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and maintenance of Applied Chillers for 1 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>quarterly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than ASHRAE Standard 180-2008.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>15625</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than ASHRAE Standard 180-2008.</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N28"/>
+  <autoFilter ref="A2:N27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1846,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1866,73 +1820,63 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>12</v>
+      <c r="B2" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Attic Stock</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Extended Warranty</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Maintenance Service</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>2</v>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Special Tool</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>26</v>
+      <c r="B7" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1946,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2008,351 +1952,390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">This Section includes administrative and procedural requirements for instructing Owner's personnel, including </t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Facilitator</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Owner training</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Needs input</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Facilitator</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystem</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystem</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+    <row r="8">
+      <c r="A8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Schedule training with Owner with at least seven days' advance notice</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Schedule training with Owner with at least seven days' advance notice</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upon completion of the work and at a time designated by the Owner's representative, provide a formal training </t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Upon completion of the work and at a time designated by the Owner's representative, provide a formal training </t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Owner training</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>15625</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and </t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Post-completion service</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1 year period</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+    <row r="11">
+      <c r="A11" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and </t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Post-completion service</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1 year period</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
@@ -2369,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2401,544 +2384,564 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>1 Precision</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1 Precision</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2 Quality</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>R11 page 10: closeout keywords but no row - review manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2 Quality</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>R11 page 208: closeout keywords but no row - review manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2 Quality</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1 intentionally blank pages skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2 Quality</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>25 candidate rows from 234 pages: Quantity Not Specified 13, O&amp;M Deliverable 7, Attic Stock 2, Extended Warranty 2, Maintenance Service 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>6 Drawings</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>0 per-unit rows totalled from drawings/counts, 5 still need a count</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>1 Precision</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>1 Precision</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>3 Labor</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>10 labor items; 0 computed from spec (0 h stated), 10 need estimator input</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>8 Div 15/16</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>R16 Division 15 Mechanical/HVAC: 9 sections, 3 with requirements, 0 flagged CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>8 Div 15/16</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>R16 Division 16 Electrical: 0 sections, 0 with requirements, 0 flagged CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>4 Delivery</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>R12 file re-opened and matches verified data (25 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>7 Language</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2 Quality</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>R15 quote has no common English words - check source</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>7 Language</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>R11 page 10: closeout keywords but no row - review manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2 Quality</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>R11 page 208: closeout keywords but no row - review manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2 Quality</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>1 intentionally blank pages skipped</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2 Quality</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>26 candidate rows from 234 pages: Quantity Not Specified 12, O&amp;M Deliverable 7, Attic Stock 2, Extended Warranty 2, Maintenance Service 2, Special Tool 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>6 Drawings</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>0 per-unit rows totalled from drawings/counts, 5 still need a count</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3 Labor</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>9 labor items; 0 computed from spec (0 h stated), 9 need estimator input</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>8 Div 15/16</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>R16 Division 15 Mechanical/HVAC: 9 sections, 3 with requirements, 0 flagged CHECK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>8 Div 15/16</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>R16 Division 16 Electrical: 0 sections, 0 with requirements, 0 flagged CHECK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>4 Delivery</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>R12 file re-opened and matches verified data (26 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>7 Language</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>R15 quote has no common English words - check source</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>7 Language</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Extraction and checks took 8 seconds</t>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Extraction and checks took 7 seconds</t>
         </is>
       </c>
     </row>
@@ -2997,270 +3000,270 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>15010</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>MECHANICAL GENERAL REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>100-108</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>1.22 RECORD DOCUMENTS; 1.7 MANUFACTURER'S INSTRUCTIONS; 1.8 WARRANTY; 1.9 TRAINING</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>OK - 3 requirement row(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>15050</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>MECHANICAL MATERIALS AND METHODS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>109-126</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>15067</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>HANGERS AND SUPPORTS</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>127-140</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>15077</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>MECHANICAL IDENTIFICATION</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>141-145</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>15080</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>MECHANICAL INSULATION</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>146-175</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>15110</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>VALVES</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>176-190</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>15181</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>HYDRONIC PIPING</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>191-204</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>1.6 EXTRA MATERIALS</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>OK - 1 requirement row(s)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>205-216</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1.05 WARRANTY; 1.06 MAINTENANCE SERVICE; 3.02 MANUFACTURER'S FIELD SERVICES</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>OK - 3 requirement row(s)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>15950</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>TESTING, ADJUSTING, AND BALANCING</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>217-234</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
@@ -3291,112 +3294,112 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>R1  Every row comes from the PDF text. Nothing is generated, guessed or taken from general knowledge.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>R2  'Spec Language (verbatim)' must appear word-for-word on the cited page (or run onto the next page). A sentence interrupted by the page header/footer is matched against the same page text with that page furniture removed - never against anything outside the cited pages.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>R3  The cited Spec Section must exist in the document and must be the section printed on that page.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>R4  Qty and Unit must be read from the quote itself. A number that is not in the quote is an error.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>R5  Qty is empty only for 'Quantity Not Specified', and that type always has an empty Qty.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>R6  No duplicate rows and no repeated quotes beyond the distinct items they contain (no padding).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>R7  There is no target row count. The document decides how many rows there are.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>R8  Quantities stated 'for each / per / of each' are NOT multiplied - the equipment count must come from the drawings or schedules and is flagged for the estimator.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>R9  Labor hours are only calculated from hours, days, persons and visits stated in the quote. Missing factors are shown as 'Needs input', never assumed.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>R10 Conflicting requirements for the same item are flagged on both rows, never silently resolved.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>R11 Pages that mention closeout items but produced no row, and pages without readable text, are listed for manual review.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>R12 The Excel file is re-opened and checked against the verified data. If any check fails, the file is not delivered.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>R13 Scanned pages are read by OCR and every row from them is marked. Rows from pages with OCR confidence below 75% are removed and the page is listed for manual review.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>R14 Per-unit quantities are totalled only from equipment tags/schedules found on the drawings or from an estimator's counts file, and the source of every count is written next to the total. 'Each type and size' is counted only from schedule columns (model/size/HP), never assumed.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>R15 The delivered file is entirely in English. Spec quotes are the original English text and are never translated or reworded. Any non-English text blocks delivery.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>R16 Every HVAC and Electrical section in the document (Divisions 23 and 26 in MasterFormat 2004, Divisions 15 and 16 in CSI 1995) is listed with its closeout subsections and row count. A section with closeout text but no extracted row is flagged CHECK; MasterFormat 2004 section numbers outside the Division 23/26 structure are flagged; a CSI 1995 five-digit number is listed but has no equivalent structure to be checked against.</t>
         </is>

--- a/spectakeoff/ECISD_Closeout_Schedule.xlsx
+++ b/spectakeoff/ECISD_Closeout_Schedule.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel</t>
+          <t>specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar docu</t>
         </is>
       </c>
       <c r="E3" s="3" t="n"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel.</t>
+          <t>Submit specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar documents.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner</t>
+          <t>Prepare and submit Project Record Documents, operation and maintenance manuals, Final Completion construction</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner.</t>
+          <t>Prepare and submit Project Record Documents, operation and maintenance manuals, Final Completion construction photographs damage or settlement surveys, property surveys, and similar final record information.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Make final changeover of permanent locks and deliver keys to Owner</t>
+          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Make final changeover of permanent locks and deliver keys to Owner.</t>
+          <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -697,50 +697,46 @@
       <c r="N5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems.</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Make final changeover of permanent locks and deliver keys to Owner</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Make final changeover of permanent locks and deliver keys to Owner.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -760,22 +756,18 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>additional copies of each warranty to include in operation and maintenance manuals</t>
+          <t>test/adjust/balance records</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>of each warranty to include in operation and maintenance manuals</t>
-        </is>
-      </c>
+      <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Provide additional copies of each warranty to include in operation and maintenance manuals.</t>
+          <t>Submit test/adjust/balance records.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -789,101 +781,77 @@
       <c r="N7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>01 78 23</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>OPERATION AND MAINTENANCE DATA</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>of each manual in final form at least 15 days before final inspection</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Manual: Submit one copy of each manual in final form at least 15 days before final inspection.</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>01 77 00</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CLOSEOUT PROCEDURES</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>pest-control final inspection report and warranty</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Submit pest-control final inspection report and warranty.</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>01 78 23</t>
+          <t>01 77 00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>OPERATION AND MAINTENANCE DATA</t>
+          <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3 copies of each corrected manual within 15 days of receipt of Engineer's comments</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>of each corrected manual within 15 days of receipt of Engineer's comments</t>
-        </is>
-      </c>
+          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Submit 3 copies of each corrected manual within 15 days of receipt of Engineer's comments.</t>
+          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -893,7 +861,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -903,39 +871,37 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>01 78 39</t>
+          <t>01 77 00</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PROJECT RECORD DOCUMENTS</t>
+          <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Number of Copies</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
+          <t>additional copies of each warranty to include in operation and maintenance manuals</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>of each warranty to include in operation and maintenance manuals</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Number of Copies: Submit one set of marked-up Record Prints.</t>
+          <t>Provide additional copies of each warranty to include in operation and maintenance manuals.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -949,62 +915,70 @@
       <c r="N10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>01 78 39</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>PROJECT RECORD DOCUMENTS</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>01 78 23</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>OPERATION AND MAINTENANCE DATA</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Record Specifications</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Record Specifications: Submit one copy of Project's Specifications, including addenda and contract modifications.</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>of each manual in final form at least 15 days before final inspection</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Manual: Submit one copy of each manual in final form at least 15 days before final inspection.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>01 78 39</t>
+          <t>01 78 23</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>PROJECT RECORD DOCUMENTS</t>
+          <t>OPERATION AND MAINTENANCE DATA</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1014,11 +988,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Record Product Data</t>
+          <t>3 copies of each corrected manual within 15 days of receipt of Engineer's comments</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1027,15 +1001,15 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>of each Product Data submittal</t>
+          <t>of each corrected manual within 15 days of receipt of Engineer's comments</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Record Product Data: Submit one copy of each Product Data submittal.</t>
+          <t>Submit 3 copies of each corrected manual within 15 days of receipt of Engineer's comments.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1053,137 +1027,141 @@
       <c r="N12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This Section includes administrative and procedural requirements for instructing Owner's personnel, including </t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>This Section includes administrative and procedural requirements for instructing Owner's personnel, including the following:</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>01 78 39</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PROJECT RECORD DOCUMENTS</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Number of Copies</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Number of Copies: Submit one set of marked-up Record Prints.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>01 78 39</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>PROJECT RECORD DOCUMENTS</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Instruction Program</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Record Specifications</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>for each training module</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Instruction Program: Submit two copies of outline of instructional program for demonstration and training, including a schedule of proposed dates, times, length of instruction time, and instructors' names for each training module.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Record Specifications: Submit one copy of Project's Specifications, including addenda and contract modifications.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>01 78 39</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>DEMONSTRATION AND TRAINING</t>
+          <t>PROJECT RECORD DOCUMENTS</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Facilitator</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>Record Product Data</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>of each Product Data submittal</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Facilitator: Engage a qualified facilitator to prepare instruction program and training modules, to coordinate instructors, and to coordinate between Contractor and Owner for number of participants, instruction times, and location.</t>
+          <t>Record Product Data: Submit one copy of each Product Data submittal.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1193,7 +1171,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -1213,23 +1191,33 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystem</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>Instruction Program</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>for each training module</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystems, and equipment not part of a system.</t>
+          <t>Instruction Program: Submit two copies of outline of instructional program for demonstration and training, including a schedule of proposed dates, times, length of instruction time, and instructors' names for each training module.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1239,7 +1227,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L16" s="3" t="n"/>
@@ -1299,33 +1287,43 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>09911</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>DEMONSTRATION AND TRAINING</t>
+          <t>EXTERIOR PAINTING</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Schedule training with Owner with at least seven days' advance notice</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
+          <t>Paint</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>of each material and color applied</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Schedule training with Owner with at least seven days' advance notice.</t>
+          <t>Paint: 5 percent, but not less than 1 gal. of each material and color applied.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1335,7 +1333,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -1345,12 +1343,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>09911</t>
+          <t>09912</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>EXTERIOR PAINTING</t>
+          <t>INTERIOR PAINTING</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1364,7 +1362,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1377,11 +1375,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Paint: 5 percent, but not less than 1 gal. of each material and color applied.</t>
+          <t>Paint: 2 percent, but not less than 1 gal. (3.8 L) of each material and color applied.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1401,39 +1399,39 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>09912</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>INTERIOR PAINTING</t>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Paint</t>
+          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Paint: 2 percent, but not less than 1 gal.</t>
+          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from date of acceptance of the job.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1447,98 +1445,98 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>15010</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>MECHANICAL GENERAL REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from date of acceptance of the job.</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training session for the Owner's operating personnel to include location, operation, and maintenance of all mechanical equipment and systems.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Revise, certify accuracy, and provide two final sets to the Architect</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Revise, certify accuracy, and provide two final sets to the Architect.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL GENERAL REQUIREMENTS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Upon completion of the work and at a time designated by the Owner's representative, provide a formal training </t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training session for the Owner's operating personnel to include location, operation, and maintenance of all mechanical equipment and systems.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1700,7 +1698,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and </t>
+          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -1826,7 +1824,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1836,7 +1834,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1890,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1965,12 +1963,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>See Division 01 Section "Demonstration and Training" for requirements for instructing Owner's personnel</t>
+          <t>specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar docu</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -1992,7 +1990,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -2031,7 +2029,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -2039,11 +2037,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This Section includes administrative and procedural requirements for instructing Owner's personnel, including </t>
+          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2070,19 +2068,19 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Facilitator</t>
+          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2109,29 +2107,29 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Engage qualified instructors to instruct Owner's personnel to adjust, operate, and maintain systems, subsystem</t>
+          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 year period</t>
         </is>
       </c>
       <c r="G6" s="4" t="n"/>
@@ -2148,29 +2146,29 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
+          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="G7" s="4" t="n"/>
@@ -2180,162 +2178,6 @@
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Schedule training with Owner with at least seven days' advance notice</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Owner training</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Upon completion of the work and at a time designated by the Owner's representative, provide a formal training </t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Owner training</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>15625</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and </t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Post-completion service</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1 year period</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>15625</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Post-completion service</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
@@ -2352,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2237,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -2415,7 +2257,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -2435,7 +2277,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -2455,7 +2297,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -2475,7 +2317,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -2486,7 +2328,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2 Quality</t>
+          <t>1 Precision</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2494,14 +2336,12 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>R11 page 10: closeout keywords but no row - review manually</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2363,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R11 page 208: closeout keywords but no row - review manually</t>
+          <t>R11 page 10: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2375,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2545,7 +2385,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1 intentionally blank pages skipped</t>
+          <t>R11 page 208: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -2567,14 +2407,14 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>25 candidate rows from 234 pages: Quantity Not Specified 13, O&amp;M Deliverable 7, Attic Stock 2, Extended Warranty 2, Maintenance Service 1</t>
+          <t>1 intentionally blank pages skipped</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>6 Drawings</t>
+          <t>2 Quality</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2589,27 +2429,29 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>0 per-unit rows totalled from drawings/counts, 5 still need a count</t>
+          <t>25 candidate rows from 234 pages: Quantity Not Specified 12, O&amp;M Deliverable 8, Attic Stock 2, Extended Warranty 2, Maintenance Service 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>6 Drawings</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>0 per-unit rows totalled from drawings/counts, 6 still need a count</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2467,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -2645,7 +2487,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
@@ -2665,7 +2507,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -2685,7 +2527,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -2705,7 +2547,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -2725,7 +2567,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -2741,62 +2583,68 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>20</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>6 labor items; 0 computed from spec (0 h stated), 6 need estimator input</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>8 Div 15/16</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>24</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R16 Division 15 Mechanical/HVAC: 9 sections, 3 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>8 Div 15/16</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>25</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R16 Division 16 Electrical: 0 sections, 0 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>4 Delivery</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2811,14 +2659,14 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10 labor items; 0 computed from spec (0 h stated), 10 need estimator input</t>
+          <t>R12 file re-opened and matches verified data (25 rows)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>8 Div 15/16</t>
+          <t>7 Language</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2833,14 +2681,14 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>R16 Division 15 Mechanical/HVAC: 9 sections, 3 with requirements, 0 flagged CHECK</t>
+          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>8 Div 15/16</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2854,92 +2702,6 @@
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>R16 Division 16 Electrical: 0 sections, 0 with requirements, 0 flagged CHECK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>4 Delivery</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>R12 file re-opened and matches verified data (25 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>7 Language</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>R15 quote has no common English words - check source</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>7 Language</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Extraction and checks took 7 seconds</t>
         </is>
@@ -3021,11 +2783,11 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>OK - 3 requirement row(s)</t>
+          <t>OK - 4 requirement row(s)</t>
         </is>
       </c>
     </row>

--- a/spectakeoff/ECISD_Closeout_Schedule.xlsx
+++ b/spectakeoff/ECISD_Closeout_Schedule.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,10 +97,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source: ECISD.pdf (234 pages) - 25 requirements. Every quote verified word-for-word against the cited page.</t>
+          <t>Source: ECISD.pdf (234 pages) - 30 requirements. Every quote verified word-for-word against the cited page.</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>01 77 00</t>
+          <t>01 73 20</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>CLOSEOUT PROCEDURES</t>
+          <t>SELECTIVE DEMOLITION</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -584,30 +584,26 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar docu</t>
+          <t>Landfill Records</t>
         </is>
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Submit specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar documents.</t>
+          <t>Landfill Records: Indicate receipt and acceptance of hazardous wastes by a landfill facility licensed to accept hazardous wastes.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
@@ -630,7 +626,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Prepare and submit Project Record Documents, operation and maintenance manuals, Final Completion construction</t>
+          <t>specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar docu</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
@@ -641,186 +637,190 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Prepare and submit Project Record Documents, operation and maintenance manuals, Final Completion construction photographs damage or settlement surveys, property surveys, and similar final record information.</t>
+          <t>Submit specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar documents.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Prepare and submit Project Record Documents, operation and maintenance manuals, Final Completion construction</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Prepare and submit Project Record Documents, operation and maintenance manuals, Final Completion construction photographs damage or settlement surveys, property surveys, and similar final record information.</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>01 77 00</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT PROCEDURES</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="n">
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Deliver tools, spare parts, extra materials, and similar items to location designated by Owner.</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Make final changeover of permanent locks and deliver keys to Owner</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="n">
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Make final changeover of permanent locks and deliver keys to Owner.</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>test/adjust/balance records</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="n">
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Submit test/adjust/balance records.</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>01 77 00</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CLOSEOUT PROCEDURES</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>pest-control final inspection report and warranty</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Submit pest-control final inspection report and warranty.</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
+          <t>pest-control final inspection report and warranty</t>
         </is>
       </c>
       <c r="E9" s="3" t="n"/>
@@ -851,19 +851,15 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems.</t>
+          <t>Submit pest-control final inspection report and warranty.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
@@ -886,30 +882,30 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>additional copies of each warranty to include in operation and maintenance manuals</t>
+          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>of each warranty to include in operation and maintenance manuals</t>
-        </is>
-      </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Provide additional copies of each warranty to include in operation and maintenance manuals.</t>
+          <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
@@ -917,124 +913,114 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>01 78 23</t>
+          <t>01 77 00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPERATION AND MAINTENANCE DATA</t>
+          <t>CLOSEOUT PROCEDURES</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
+          <t>additional copies of each warranty to include in operation and maintenance manuals</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>of each manual in final form at least 15 days before final inspection</t>
+          <t>of each warranty to include in operation and maintenance manuals</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Manual: Submit one copy of each manual in final form at least 15 days before final inspection.</t>
+          <t>Provide additional copies of each warranty to include in operation and maintenance manuals.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>01 78 23</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>OPERATION AND MAINTENANCE DATA</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>3 copies of each corrected manual within 15 days of receipt of Engineer's comments</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>of each corrected manual within 15 days of receipt of Engineer's comments</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>of each manual in final form at least 15 days before final inspection</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Submit 3 copies of each corrected manual within 15 days of receipt of Engineer's comments.</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Manual: Submit one copy of each manual in final form at least 15 days before final inspection.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>01 78 39</t>
+          <t>01 78 23</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PROJECT RECORD DOCUMENTS</t>
+          <t>OPERATION AND MAINTENANCE DATA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1044,83 +1030,85 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Number of Copies</t>
+          <t>3 copies of each corrected manual within 15 days of receipt of Engineer's comments</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>of each corrected manual within 15 days of receipt of Engineer's comments</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Number of Copies: Submit one set of marked-up Record Prints.</t>
+          <t>Submit 3 copies of each corrected manual within 15 days of receipt of Engineer's comments.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>01 78 39</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>PROJECT RECORD DOCUMENTS</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Record Specifications</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Record Specifications: Submit one copy of Project's Specifications, including addenda and contract modifications.</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>01 78 23</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>OPERATION AND MAINTENANCE DATA</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Spare Parts List and Source Information</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Spare Parts List and Source Information: Include lists of replacement and repair parts, with parts identified and cross-referenced to manufacturers' maintenance documentation and local sources of maintenance materials and related services.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1140,7 +1128,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Record Product Data</t>
+          <t>Number of Copies</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -1148,32 +1136,24 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>of each Product Data submittal</t>
-        </is>
-      </c>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="n">
         <v>73</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Record Product Data: Submit one copy of each Product Data submittal.</t>
+          <t>Number of Copies: Submit one set of marked-up Record Prints.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3" t="n"/>
@@ -1181,12 +1161,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>01 78 39</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>DEMONSTRATION AND TRAINING</t>
+          <t>PROJECT RECORD DOCUMENTS</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1196,202 +1176,186 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Instruction Program</t>
+          <t>Record Specifications</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>for each training module</t>
-        </is>
-      </c>
+      <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Instruction Program: Submit two copies of outline of instructional program for demonstration and training, including a schedule of proposed dates, times, length of instruction time, and instructors' names for each training module.</t>
+          <t>Record Specifications: Submit one copy of Project's Specifications, including addenda and contract modifications.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>01 78 39</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>PROJECT RECORD DOCUMENTS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Record Product Data</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>of each Product Data submittal</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Record Product Data: Submit one copy of each Product Data submittal.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>of each season</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season.</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Instruction Program</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>for each training module</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Instruction Program: Submit two copies of outline of instructional program for demonstration and training, including a schedule of proposed dates, times, length of instruction time, and instructors' names for each training module.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>09911</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>EXTERIOR PAINTING</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Paint</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>PCT</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>of each material and color applied</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Paint: 5 percent, but not less than 1 gal. of each material and color applied.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>09912</t>
+          <t>01 79 00</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>INTERIOR PAINTING</t>
+          <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Paint</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>PCT</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>of each material and color applied</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Paint: 2 percent, but not less than 1 gal. (3.8 L) of each material and color applied.</t>
+          <t>Maintenance: Include inspection procedures, types of cleaning agents, methods of cleaning, procedures for preventive and routine maintenance, and instruction on use of special tools.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
@@ -1399,47 +1363,49 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>01 79 00</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+          <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
+          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>of each season</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from date of acceptance of the job.</t>
+          <t>For equipment that requires seasonal operation, provide similar instruction at start of each season.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
@@ -1447,12 +1413,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>09911</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+          <t>EXTERIOR PAINTING</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1462,30 +1428,26 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training</t>
+          <t>extra materials, from the same product run, that match products installed and that are packaged with protectiv</t>
         </is>
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training session for the Owner's operating personnel to include location, operation, and maintenance of all mechanical equipment and systems.</t>
+          <t>Furnish extra materials, from the same product run, that match products installed and that are packaged with protective covering for storage and identified with labels describing contents.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3" t="n"/>
@@ -1493,301 +1455,549 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>09911</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+          <t>EXTERIOR PAINTING</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Revise, certify accuracy, and provide two final sets to the Architect</t>
+          <t>Paint</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>of each material and color applied</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Revise, certify accuracy, and provide two final sets to the Architect.</t>
+          <t>Paint: 5 percent, but not less than 1 gal. of each material and color applied.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>MECHANICAL GENERAL REQUIREMENTS</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Owner's Manual</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Owner's Manual: Prior to final acceptance, provide two bound volumes to the Architect.</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>09912</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>INTERIOR PAINTING</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>extra materials that match products installed and that are packaged with protective covering for storage and i</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Furnish extra materials that match products installed and that are packaged with protective covering for storage and identified with labels describing contents.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>09912</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HYDRONIC PIPING</t>
+          <t>INTERIOR PAINTING</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Water Treatment Chemicals</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr"/>
+          <t>Paint</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>from date of Substantial Completion</t>
+          <t>of each material and color applied</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Water Treatment Chemicals: Furnish sufficient chemicals for initial system startup and for preventive maintenance for one year from date of Substantial Completion.</t>
+          <t>Paint: 2 percent, but not less than 1 gal. (3.8 L) of each material and color applied.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>15625</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Extended Warranty</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whi</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Provide a full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whichever occurs first.</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>The contractor shall warranty his work against defective materials and workmanship for a period of 1-year from date of acceptance of the job.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>15625</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and maintenance of Applied Chillers for 1 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training session for the Owner's operating personnel to include location, operation, and maintenance of all mechanical equipment and systems.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>quarterly - count not stated in this sentence, estimator must compute it</t>
-        </is>
-      </c>
+          <t>Revise, certify accuracy, and provide two final sets to the Architect</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="n">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than ASHRAE Standard 180-2008.</t>
+          <t>Revise, certify accuracy, and provide two final sets to the Architect.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>MECHANICAL GENERAL REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Owner's Manual</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Owner's Manual: Prior to final acceptance, provide two bound volumes to the Architect.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>15181</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>HYDRONIC PIPING</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Water Treatment Chemicals</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>from date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Water Treatment Chemicals: Furnish sufficient chemicals for initial system startup and for preventive maintenance for one year from date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>15625</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whi</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Provide a full parts, labor and refrigerant warranty for five years from startup or 66 months from factory shipment, whichever occurs first.</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>15625</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and maintenance of Applied Chillers for 1 years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>15625</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>quarterly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than ASHRAE Standard 180-2008.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N27"/>
+  <autoFilter ref="A2:N32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1818,63 +2028,63 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>12</v>
+      <c r="B2" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Attic Stock</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Extended Warranty</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Maintenance Service</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>25</v>
+      <c r="B7" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1950,234 +2160,234 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>specific warranties, workmanship bonds, maintenance service agreements, final certifications, and similar docu</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Post-completion service</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>01 77 00</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Instruct Owner's personnel in operation, adjustment, and maintenance of products, equipment, and systems</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>For equipment that requires seasonal operation, provide similar instruction at start of each season</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>15010</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Upon completion of the work and at a time designated by the Owner's representative, provide a formal training</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Owner training</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>In conjunction with and supporting Factory warranty OEM shall furnish complete factory authorized service and</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Post-completion service</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1 year period</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>OEM shall provide and report quarterly, semiannual, and annual maintenance in compliance with or better than A</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Post-completion service</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Needs input</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
@@ -2226,484 +2436,484 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>1 Precision</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2 Quality</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>R11 page 10: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2 Quality</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>R11 page 208: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2 Quality</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>1 intentionally blank pages skipped</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2 Quality</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>25 candidate rows from 234 pages: Quantity Not Specified 12, O&amp;M Deliverable 8, Attic Stock 2, Extended Warranty 2, Maintenance Service 1</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>30 candidate rows from 234 pages: Quantity Not Specified 17, O&amp;M Deliverable 8, Attic Stock 2, Extended Warranty 2, Maintenance Service 1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>6 Drawings</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>0 per-unit rows totalled from drawings/counts, 6 still need a count</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>3 Labor</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>6 labor items; 0 computed from spec (0 h stated), 6 need estimator input</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>8 Div 15/16</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>R16 Division 15 Mechanical/HVAC: 9 sections, 3 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>8 Div 15/16</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>R16 Division 16 Electrical: 0 sections, 0 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>4 Delivery</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>R12 file re-opened and matches verified data (25 rows)</t>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>R12 file re-opened and matches verified data (30 rows)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>7 Language</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Extraction and checks took 7 seconds</t>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Extraction and checks took 6 seconds</t>
         </is>
       </c>
     </row>
@@ -2762,270 +2972,270 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>15010</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>MECHANICAL GENERAL REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>100-108</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>1.22 RECORD DOCUMENTS; 1.7 MANUFACTURER'S INSTRUCTIONS; 1.8 WARRANTY; 1.9 TRAINING</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>OK - 4 requirement row(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>15050</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>MECHANICAL MATERIALS AND METHODS</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>109-126</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>15067</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>HANGERS AND SUPPORTS</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>127-140</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>15077</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>MECHANICAL IDENTIFICATION</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>141-145</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>15080</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>MECHANICAL INSULATION</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>146-175</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>15110</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>VALVES</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>176-190</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>15181</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>HYDRONIC PIPING</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>191-204</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>1.6 EXTRA MATERIALS</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>OK - 1 requirement row(s)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>CENTRIFUGAL WATER-COOLED CHILLERS</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>205-216</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>1.05 WARRANTY; 1.06 MAINTENANCE SERVICE; 3.02 MANUFACTURER'S FIELD SERVICES</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>OK - 3 requirement row(s)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>15950</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>TESTING, ADJUSTING, AND BALANCING</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>217-234</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>No closeout requirements in this section</t>
         </is>
@@ -3056,112 +3266,112 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>R1  Every row comes from the PDF text. Nothing is generated, guessed or taken from general knowledge.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>R2  'Spec Language (verbatim)' must appear word-for-word on the cited page (or run onto the next page). A sentence interrupted by the page header/footer is matched against the same page text with that page furniture removed - never against anything outside the cited pages.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>R3  The cited Spec Section must exist in the document and must be the section printed on that page.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>R4  Qty and Unit must be read from the quote itself. A number that is not in the quote is an error.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>R5  Qty is empty only for 'Quantity Not Specified', and that type always has an empty Qty.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>R6  No duplicate rows and no repeated quotes beyond the distinct items they contain (no padding).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>R7  There is no target row count. The document decides how many rows there are.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>R8  Quantities stated 'for each / per / of each' are NOT multiplied - the equipment count must come from the drawings or schedules and is flagged for the estimator.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>R9  Labor hours are only calculated from hours, days, persons and visits stated in the quote. Missing factors are shown as 'Needs input', never assumed.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>R10 Conflicting requirements for the same item are flagged on both rows, never silently resolved.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>R11 Pages that mention closeout items but produced no row, and pages without readable text, are listed for manual review.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>R12 The Excel file is re-opened and checked against the verified data. If any check fails, the file is not delivered.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>R13 Scanned pages are read by OCR and every row from them is marked. Rows from pages with OCR confidence below 75% are removed and the page is listed for manual review.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>R14 Per-unit quantities are totalled only from equipment tags/schedules found on the drawings or from an estimator's counts file, and the source of every count is written next to the total. 'Each type and size' is counted only from schedule columns (model/size/HP), never assumed.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>R15 The delivered file is entirely in English. Spec quotes are the original English text and are never translated or reworded. Any non-English text blocks delivery.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>R16 Every HVAC and Electrical section in the document (Divisions 23 and 26 in MasterFormat 2004, Divisions 15 and 16 in CSI 1995) is listed with its closeout subsections and row count. A section with closeout text but no extracted row is flagged CHECK; MasterFormat 2004 section numbers outside the Division 23/26 structure are flagged; a CSI 1995 five-digit number is listed but has no equivalent structure to be checked against.</t>
         </is>
